--- a/tools/importer/reports/import-resource-detail.report.xlsx
+++ b/tools/importer/reports/import-resource-detail.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-25T23:01:01.616Z</t>
+    <t>2026-03-28T19:35:31.451Z</t>
   </si>
   <si>
     <t>Cvent | Event Platform for In-person, Virtual, and Hybrid Events &amp; Webinars</t>
@@ -73,7 +73,7 @@
     <t>training-certification</t>
   </si>
   <si>
-    <t>2026-03-28T17:23:20.419Z</t>
+    <t>2026-03-28T19:39:53.753Z</t>
   </si>
   <si>
     <t>Cvent Academy | Cvent</t>
@@ -94,7 +94,7 @@
     <t>company-info</t>
   </si>
   <si>
-    <t>2026-03-28T17:13:17.611Z</t>
+    <t>2026-03-28T19:38:42.107Z</t>
   </si>
   <si>
     <t>Awards and Recognition - Event Management | Cvent</t>
@@ -109,7 +109,7 @@
     <t>en/become-partner</t>
   </si>
   <si>
-    <t>2026-03-28T17:13:30.225Z</t>
+    <t>2026-03-28T19:38:56.233Z</t>
   </si>
   <si>
     <t>Partner Program - Join the Cvent Partner Program | Cvent</t>
@@ -130,7 +130,7 @@
     <t>resource-listing</t>
   </si>
   <si>
-    <t>2026-03-28T17:09:52.922Z</t>
+    <t>2026-03-28T19:38:05.603Z</t>
   </si>
   <si>
     <t>Your Hub for Meetings, Hospitality, and Event Excellence | Cvent Blog</t>
@@ -148,7 +148,7 @@
     <t>en/case-studies</t>
   </si>
   <si>
-    <t>2026-03-28T17:09:59.953Z</t>
+    <t>2026-03-28T19:38:11.569Z</t>
   </si>
   <si>
     <t>Cvent Customer Success Stories &amp; Reviews</t>
@@ -166,7 +166,7 @@
     <t>en/company</t>
   </si>
   <si>
-    <t>2026-03-28T17:13:11.854Z</t>
+    <t>2026-03-28T19:38:37.479Z</t>
   </si>
   <si>
     <t>Company Overview | Cvent</t>
@@ -184,7 +184,7 @@
     <t>contact-demo</t>
   </si>
   <si>
-    <t>2026-03-28T17:17:02.216Z</t>
+    <t>2026-03-28T19:39:16.088Z</t>
   </si>
   <si>
     <t>Contact Us | Cvent</t>
@@ -199,7 +199,7 @@
     <t>en/cvent-certification</t>
   </si>
   <si>
-    <t>2026-03-28T17:23:26.924Z</t>
+    <t>2026-03-28T19:40:02.106Z</t>
   </si>
   <si>
     <t>Cvent Certification | Cvent</t>
@@ -217,7 +217,7 @@
     <t>en/cvent-news-and-press-releases</t>
   </si>
   <si>
-    <t>2026-03-28T17:10:19.563Z</t>
+    <t>2026-03-28T19:38:31.447Z</t>
   </si>
   <si>
     <t>Cvent News &amp; Press Releases | Newsroom | Cvent</t>
@@ -238,7 +238,7 @@
     <t>product-platform</t>
   </si>
   <si>
-    <t>2026-03-28T10:11:11.208Z</t>
+    <t>2026-03-28T19:36:17.192Z</t>
   </si>
   <si>
     <t>CventIQ: AI Solutions for Events</t>
@@ -256,7 +256,7 @@
     <t>en/event-management-software</t>
   </si>
   <si>
-    <t>2026-03-28T10:10:28.519Z</t>
+    <t>2026-03-28T19:35:39.612Z</t>
   </si>
   <si>
     <t>Online Event Management Software | Cvent</t>
@@ -274,7 +274,7 @@
     <t>en/event-types</t>
   </si>
   <si>
-    <t>2026-03-28T10:11:02.043Z</t>
+    <t>2026-03-28T19:36:10.048Z</t>
   </si>
   <si>
     <t>404 | Cvent</t>
@@ -289,7 +289,7 @@
     <t>en/management-team</t>
   </si>
   <si>
-    <t>2026-03-28T17:13:25.006Z</t>
+    <t>2026-03-28T19:38:49.010Z</t>
   </si>
   <si>
     <t>Management Team | Senior Leadership | Cvent</t>
@@ -307,7 +307,7 @@
     <t>legal</t>
   </si>
   <si>
-    <t>2026-03-28T17:22:50.655Z</t>
+    <t>2026-03-28T19:39:27.745Z</t>
   </si>
   <si>
     <t>Cvent Privacy Policy | Cvent</t>
@@ -322,7 +322,7 @@
     <t>en/product-terms-of-use</t>
   </si>
   <si>
-    <t>2026-03-28T17:22:56.079Z</t>
+    <t>2026-03-28T19:39:34.504Z</t>
   </si>
   <si>
     <t>Terms of Use for Cvent Products | Cvent</t>
@@ -340,7 +340,7 @@
     <t>en/products</t>
   </si>
   <si>
-    <t>2026-03-28T10:10:53.416Z</t>
+    <t>2026-03-28T19:36:03.690Z</t>
   </si>
   <si>
     <t>Events &amp; Venue Management Products | Cvent</t>
@@ -358,7 +358,7 @@
     <t>en/request-demo</t>
   </si>
   <si>
-    <t>2026-03-28T17:16:54.623Z</t>
+    <t>2026-03-28T19:39:09.188Z</t>
   </si>
   <si>
     <t>Cvent Demo | Cvent</t>
@@ -373,7 +373,7 @@
     <t>en/resources</t>
   </si>
   <si>
-    <t>2026-03-28T17:10:13.829Z</t>
+    <t>2026-03-28T19:38:26.017Z</t>
   </si>
   <si>
     <t>Content Library | Resources | Cvent</t>
@@ -391,7 +391,7 @@
     <t>en/security</t>
   </si>
   <si>
-    <t>2026-03-28T17:13:37.908Z</t>
+    <t>2026-03-28T19:39:03.024Z</t>
   </si>
   <si>
     <t>Event Data Security for Customers | Cvent</t>
@@ -412,7 +412,7 @@
     <t>supplier-venue</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:20.600Z</t>
+    <t>2026-03-28T19:37:19.532Z</t>
   </si>
   <si>
     <t>Supplier and Venue Management Solutions | Cvent</t>
@@ -427,7 +427,7 @@
     <t>en/upcoming-webinars</t>
   </si>
   <si>
-    <t>2026-03-28T17:10:07.602Z</t>
+    <t>2026-03-28T19:38:17.968Z</t>
   </si>
   <si>
     <t>Upcoming Events</t>
@@ -442,7 +442,7 @@
     <t>en/website-terms-use</t>
   </si>
   <si>
-    <t>2026-03-28T17:23:02.952Z</t>
+    <t>2026-03-28T19:39:41.775Z</t>
   </si>
   <si>
     <t>Website Terms of Use | Cvent</t>
@@ -457,7 +457,7 @@
     <t>en/company/legal</t>
   </si>
   <si>
-    <t>2026-03-28T17:23:08.512Z</t>
+    <t>2026-03-28T19:39:47.502Z</t>
   </si>
   <si>
     <t>Cvent Legal</t>
@@ -472,7 +472,7 @@
     <t>en/contact/support</t>
   </si>
   <si>
-    <t>2026-03-28T17:17:10.105Z</t>
+    <t>2026-03-28T19:39:22.940Z</t>
   </si>
   <si>
     <t>Cvent Support</t>
@@ -490,7 +490,7 @@
     <t>en/event-management-software/cvent-integrations</t>
   </si>
   <si>
-    <t>2026-03-28T10:10:35.751Z</t>
+    <t>2026-03-28T19:35:45.911Z</t>
   </si>
   <si>
     <t>Meeting &amp; Events Tools Integration With Cvent</t>
@@ -508,7 +508,7 @@
     <t>en/event-management-software/cvent-pricing</t>
   </si>
   <si>
-    <t>2026-03-28T10:10:45.444Z</t>
+    <t>2026-03-28T19:35:54.043Z</t>
   </si>
   <si>
     <t>Cvent Pricing | Request a Quote</t>
@@ -529,7 +529,7 @@
     <t>product-feature</t>
   </si>
   <si>
-    <t>2026-03-28T09:37:00.519Z</t>
+    <t>2026-03-28T19:37:13.608Z</t>
   </si>
   <si>
     <t>Create Accessible Events with Cvent | Cvent</t>
@@ -547,7 +547,7 @@
     <t>en/event-marketing-management/cvent-essentials</t>
   </si>
   <si>
-    <t>2026-03-28T09:36:17.225Z</t>
+    <t>2026-03-28T19:36:50.943Z</t>
   </si>
   <si>
     <t>Cvent Essentials | Cvent</t>
@@ -565,7 +565,7 @@
     <t>en/event-marketing-management/cvent-supplier-network</t>
   </si>
   <si>
-    <t>2026-03-28T09:36:41.555Z</t>
+    <t>2026-03-28T19:37:07.548Z</t>
   </si>
   <si>
     <t>Free Venue Sourcing Tool | Cvent</t>
@@ -583,7 +583,7 @@
     <t>en/event-marketing-management/event-registration-software</t>
   </si>
   <si>
-    <t>2026-03-28T09:35:54.661Z</t>
+    <t>2026-03-28T19:36:28.175Z</t>
   </si>
   <si>
     <t>Online Event Registration Software | Cvent</t>
@@ -601,7 +601,7 @@
     <t>en/event-marketing-management/mobile-event-apps</t>
   </si>
   <si>
-    <t>2026-03-28T09:36:03.641Z</t>
+    <t>2026-03-28T19:36:35.198Z</t>
   </si>
   <si>
     <t>AI-Powered Event App | Cvent</t>
@@ -619,7 +619,7 @@
     <t>en/event-marketing-management/onarrival-event-check-in-software</t>
   </si>
   <si>
-    <t>2026-03-28T09:36:35.560Z</t>
+    <t>2026-03-28T19:36:59.498Z</t>
   </si>
   <si>
     <t>Onsite Event Check-in and Badging Solutions | Cvent</t>
@@ -637,7 +637,7 @@
     <t>en/event-marketing-management/webinar-platform</t>
   </si>
   <si>
-    <t>2026-03-28T09:36:10.130Z</t>
+    <t>2026-03-28T19:36:44.137Z</t>
   </si>
   <si>
     <t>Best Webinar Platform - Deliver Interactive Webinars | Cvent</t>
@@ -655,7 +655,7 @@
     <t>en/supplier-venue/business-travel-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:58.656Z</t>
+    <t>2026-03-28T19:37:59.258Z</t>
   </si>
   <si>
     <t>Business Travel Solutions | Cvent</t>
@@ -673,7 +673,7 @@
     <t>en/supplier-venue/group-marketing-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:29.315Z</t>
+    <t>2026-03-28T19:37:27.479Z</t>
   </si>
   <si>
     <t>Group Marketing Solutions | Increase Visibility &amp; Drive Business | Cvent</t>
@@ -691,7 +691,7 @@
     <t>en/supplier-venue/group-operations-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:44.445Z</t>
+    <t>2026-03-28T19:37:41.089Z</t>
   </si>
   <si>
     <t>Hotel Operations Management Solutions | Cvent</t>
@@ -706,7 +706,7 @@
     <t>en/supplier-venue/group-sales-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:37.105Z</t>
+    <t>2026-03-28T19:37:35.031Z</t>
   </si>
   <si>
     <t>Hotel Sales Solutions | Maximize Sales &amp; Streamline Bookings | Cvent</t>
@@ -724,7 +724,7 @@
     <t>en/supplier-venue/hotel-business-intelligence</t>
   </si>
   <si>
-    <t>2026-03-28T12:45:50.265Z</t>
+    <t>2026-03-28T19:37:49.586Z</t>
   </si>
   <si>
     <t>Hotel Business Intelligence Software | Data-Driven Growth | Cvent</t>
@@ -742,7 +742,7 @@
     <t>resource-detail</t>
   </si>
   <si>
-    <t>2026-03-28T17:23:40.420Z</t>
+    <t>2026-03-28T19:40:08.779Z</t>
   </si>
   <si>
     <t>Your Top Event Trends for 2026 | Cvent</t>

--- a/tools/importer/reports/import-resource-detail.report.xlsx
+++ b/tools/importer/reports/import-resource-detail.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-28T19:35:31.451Z</t>
+    <t>2026-03-28T22:23:49.715Z</t>
   </si>
   <si>
     <t>Cvent | Event Platform for In-person, Virtual, and Hybrid Events &amp; Webinars</t>
@@ -94,7 +94,7 @@
     <t>company-info</t>
   </si>
   <si>
-    <t>2026-03-28T19:38:42.107Z</t>
+    <t>2026-03-28T22:26:30.336Z</t>
   </si>
   <si>
     <t>Awards and Recognition - Event Management | Cvent</t>
@@ -109,7 +109,7 @@
     <t>en/become-partner</t>
   </si>
   <si>
-    <t>2026-03-28T19:38:56.233Z</t>
+    <t>2026-03-28T22:26:42.882Z</t>
   </si>
   <si>
     <t>Partner Program - Join the Cvent Partner Program | Cvent</t>
@@ -166,7 +166,7 @@
     <t>en/company</t>
   </si>
   <si>
-    <t>2026-03-28T19:38:37.479Z</t>
+    <t>2026-03-28T22:26:22.910Z</t>
   </si>
   <si>
     <t>Company Overview | Cvent</t>
@@ -184,7 +184,7 @@
     <t>contact-demo</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:16.088Z</t>
+    <t>2026-03-28T22:27:02.879Z</t>
   </si>
   <si>
     <t>Contact Us | Cvent</t>
@@ -238,7 +238,7 @@
     <t>product-platform</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:17.192Z</t>
+    <t>2026-03-28T22:25:34.453Z</t>
   </si>
   <si>
     <t>CventIQ: AI Solutions for Events</t>
@@ -256,7 +256,7 @@
     <t>en/event-management-software</t>
   </si>
   <si>
-    <t>2026-03-28T19:35:39.612Z</t>
+    <t>2026-03-28T22:24:54.167Z</t>
   </si>
   <si>
     <t>Online Event Management Software | Cvent</t>
@@ -274,7 +274,7 @@
     <t>en/event-types</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:10.048Z</t>
+    <t>2026-03-28T22:25:26.079Z</t>
   </si>
   <si>
     <t>404 | Cvent</t>
@@ -289,7 +289,7 @@
     <t>en/management-team</t>
   </si>
   <si>
-    <t>2026-03-28T19:38:49.010Z</t>
+    <t>2026-03-28T22:26:37.467Z</t>
   </si>
   <si>
     <t>Management Team | Senior Leadership | Cvent</t>
@@ -307,7 +307,7 @@
     <t>legal</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:27.745Z</t>
+    <t>2026-03-28T22:27:16.161Z</t>
   </si>
   <si>
     <t>Cvent Privacy Policy | Cvent</t>
@@ -322,7 +322,7 @@
     <t>en/product-terms-of-use</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:34.504Z</t>
+    <t>2026-03-28T22:27:21.983Z</t>
   </si>
   <si>
     <t>Terms of Use for Cvent Products | Cvent</t>
@@ -340,7 +340,7 @@
     <t>en/products</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:03.690Z</t>
+    <t>2026-03-28T22:25:19.343Z</t>
   </si>
   <si>
     <t>Events &amp; Venue Management Products | Cvent</t>
@@ -358,7 +358,7 @@
     <t>en/request-demo</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:09.188Z</t>
+    <t>2026-03-28T22:26:54.796Z</t>
   </si>
   <si>
     <t>Cvent Demo | Cvent</t>
@@ -391,7 +391,7 @@
     <t>en/security</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:03.024Z</t>
+    <t>2026-03-28T22:26:49.737Z</t>
   </si>
   <si>
     <t>Event Data Security for Customers | Cvent</t>
@@ -412,7 +412,7 @@
     <t>supplier-venue</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:19.532Z</t>
+    <t>2026-03-28T22:25:41.274Z</t>
   </si>
   <si>
     <t>Supplier and Venue Management Solutions | Cvent</t>
@@ -442,7 +442,7 @@
     <t>en/website-terms-use</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:41.775Z</t>
+    <t>2026-03-28T22:27:27.800Z</t>
   </si>
   <si>
     <t>Website Terms of Use | Cvent</t>
@@ -457,7 +457,7 @@
     <t>en/company/legal</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:47.502Z</t>
+    <t>2026-03-28T22:27:33.832Z</t>
   </si>
   <si>
     <t>Cvent Legal</t>
@@ -472,7 +472,7 @@
     <t>en/contact/support</t>
   </si>
   <si>
-    <t>2026-03-28T19:39:22.940Z</t>
+    <t>2026-03-28T22:27:10.203Z</t>
   </si>
   <si>
     <t>Cvent Support</t>
@@ -490,7 +490,7 @@
     <t>en/event-management-software/cvent-integrations</t>
   </si>
   <si>
-    <t>2026-03-28T19:35:45.911Z</t>
+    <t>2026-03-28T22:25:01.555Z</t>
   </si>
   <si>
     <t>Meeting &amp; Events Tools Integration With Cvent</t>
@@ -508,7 +508,7 @@
     <t>en/event-management-software/cvent-pricing</t>
   </si>
   <si>
-    <t>2026-03-28T19:35:54.043Z</t>
+    <t>2026-03-28T22:25:08.947Z</t>
   </si>
   <si>
     <t>Cvent Pricing | Request a Quote</t>
@@ -529,7 +529,7 @@
     <t>product-feature</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:13.608Z</t>
+    <t>2026-03-28T22:24:47.274Z</t>
   </si>
   <si>
     <t>Create Accessible Events with Cvent | Cvent</t>
@@ -547,7 +547,7 @@
     <t>en/event-marketing-management/cvent-essentials</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:50.943Z</t>
+    <t>2026-03-28T22:24:23.084Z</t>
   </si>
   <si>
     <t>Cvent Essentials | Cvent</t>
@@ -565,7 +565,7 @@
     <t>en/event-marketing-management/cvent-supplier-network</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:07.548Z</t>
+    <t>2026-03-28T22:24:39.111Z</t>
   </si>
   <si>
     <t>Free Venue Sourcing Tool | Cvent</t>
@@ -583,7 +583,7 @@
     <t>en/event-marketing-management/event-registration-software</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:28.175Z</t>
+    <t>2026-03-28T22:23:57.919Z</t>
   </si>
   <si>
     <t>Online Event Registration Software | Cvent</t>
@@ -601,7 +601,7 @@
     <t>en/event-marketing-management/mobile-event-apps</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:35.198Z</t>
+    <t>2026-03-28T22:24:07.173Z</t>
   </si>
   <si>
     <t>AI-Powered Event App | Cvent</t>
@@ -619,7 +619,7 @@
     <t>en/event-marketing-management/onarrival-event-check-in-software</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:59.498Z</t>
+    <t>2026-03-28T22:24:31.204Z</t>
   </si>
   <si>
     <t>Onsite Event Check-in and Badging Solutions | Cvent</t>
@@ -637,7 +637,7 @@
     <t>en/event-marketing-management/webinar-platform</t>
   </si>
   <si>
-    <t>2026-03-28T19:36:44.137Z</t>
+    <t>2026-03-28T22:24:15.204Z</t>
   </si>
   <si>
     <t>Best Webinar Platform - Deliver Interactive Webinars | Cvent</t>
@@ -655,7 +655,7 @@
     <t>en/supplier-venue/business-travel-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:59.258Z</t>
+    <t>2026-03-28T22:26:17.535Z</t>
   </si>
   <si>
     <t>Business Travel Solutions | Cvent</t>
@@ -673,7 +673,7 @@
     <t>en/supplier-venue/group-marketing-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:27.479Z</t>
+    <t>2026-03-28T22:25:49.378Z</t>
   </si>
   <si>
     <t>Group Marketing Solutions | Increase Visibility &amp; Drive Business | Cvent</t>
@@ -691,7 +691,7 @@
     <t>en/supplier-venue/group-operations-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:41.089Z</t>
+    <t>2026-03-28T22:26:02.633Z</t>
   </si>
   <si>
     <t>Hotel Operations Management Solutions | Cvent</t>
@@ -706,7 +706,7 @@
     <t>en/supplier-venue/group-sales-solutions</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:35.031Z</t>
+    <t>2026-03-28T22:25:56.435Z</t>
   </si>
   <si>
     <t>Hotel Sales Solutions | Maximize Sales &amp; Streamline Bookings | Cvent</t>
@@ -724,7 +724,7 @@
     <t>en/supplier-venue/hotel-business-intelligence</t>
   </si>
   <si>
-    <t>2026-03-28T19:37:49.586Z</t>
+    <t>2026-03-28T22:26:09.880Z</t>
   </si>
   <si>
     <t>Hotel Business Intelligence Software | Data-Driven Growth | Cvent</t>
@@ -742,7 +742,7 @@
     <t>resource-detail</t>
   </si>
   <si>
-    <t>2026-03-28T19:40:08.779Z</t>
+    <t>2026-03-28T22:27:40.483Z</t>
   </si>
   <si>
     <t>Your Top Event Trends for 2026 | Cvent</t>
